--- a/output/casestudy_20260811.xlsx
+++ b/output/casestudy_20260811.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>4.840895699999237</v>
+        <v>5.265685300000769</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>5.432688900000358</v>
+        <v>5.70992699999988</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>4.976122500000201</v>
+        <v>5.267121600001701</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>4.756599799999094</v>
+        <v>4.936219899998832</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>4.641177899997274</v>
+        <v>5.170540200000687</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>4.8019103000006</v>
+        <v>5.810978300003626</v>
       </c>
     </row>
   </sheetData>
@@ -5834,7 +5834,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>거래 가능일 245일 · 등록 권장 631 kW · 연간 감축 341,921 kWh</t>
+          <t>거래 가능일 245일 · 등록 권장 236 kW · 연간 감축 14,184 kWh</t>
         </is>
       </c>
     </row>
@@ -5925,7 +5925,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>거래 가능일 245일 · 등록 권장 0 kW · 연간 감축 302,808 kWh</t>
+          <t>거래 가능일 245일 · 등록 권장 0 kW · 연간 감축 0 kWh</t>
         </is>
       </c>
     </row>
@@ -6016,7 +6016,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>거래 가능일 245일 · 등록 권장 62 kW · 연간 감축 47,157 kWh</t>
+          <t>거래 가능일 245일 · 등록 권장 7 kW · 연간 감축 443 kWh</t>
         </is>
       </c>
     </row>
@@ -6107,7 +6107,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>거래 가능일 245일 · 등록 권장 598 kW · 연간 감축 333,817 kWh</t>
+          <t>거래 가능일 245일 · 등록 권장 205 kW · 연간 감축 12,308 kWh</t>
         </is>
       </c>
     </row>
@@ -6198,7 +6198,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>거래 가능일 245일 · 등록 권장 698 kW · 연간 감축 321,538 kWh</t>
+          <t>거래 가능일 245일 · 등록 권장 335 kW · 연간 감축 20,073 kWh</t>
         </is>
       </c>
     </row>
@@ -7537,7 +7537,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4.8 초</t>
+          <t>5.3 초</t>
         </is>
       </c>
     </row>
@@ -7549,7 +7549,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>5.4 초</t>
+          <t>5.7 초</t>
         </is>
       </c>
     </row>
@@ -7561,7 +7561,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>5.0 초</t>
+          <t>5.3 초</t>
         </is>
       </c>
     </row>
@@ -7573,7 +7573,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4.8 초</t>
+          <t>4.9 초</t>
         </is>
       </c>
     </row>
@@ -7585,7 +7585,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4.6 초</t>
+          <t>5.2 초</t>
         </is>
       </c>
     </row>
@@ -7597,7 +7597,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4.8 초</t>
+          <t>5.8 초</t>
         </is>
       </c>
     </row>
@@ -7609,7 +7609,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>30.6 초</t>
+          <t>33.3 초</t>
         </is>
       </c>
     </row>
